--- a/DRIVE/3. Operações/3.1 Projetos/Lista entregaveis projetos.xlsx
+++ b/DRIVE/3. Operações/3.1 Projetos/Lista entregaveis projetos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\MINDSET\DRIVE\3. Operações\3.1 Projetos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11626064-0B5C-4D36-BEBE-F084A2FBDECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{392D1C06-36B3-4EE2-9BDB-D8AFD666CB30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="51">
   <si>
     <t>Nº</t>
   </si>
@@ -187,6 +187,9 @@
   </si>
   <si>
     <t>INDEFINIDA</t>
+  </si>
+  <si>
+    <t>Espera fornecedor, aguardar feeback</t>
   </si>
 </sst>
 </file>
@@ -670,22 +673,22 @@
     <xf numFmtId="0" fontId="19" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -967,39 +970,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36"/>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
+      <c r="A1" s="38"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
     </row>
     <row r="2" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
     </row>
     <row r="3" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="38"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
     </row>
     <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
@@ -1203,15 +1206,15 @@
       <c r="I14" s="6"/>
     </row>
     <row r="16" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1237,35 +1240,35 @@
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
     <col min="7" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.21875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36"/>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
+      <c r="A1" s="38"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
     </row>
     <row r="2" spans="1:14" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
       <c r="L2" s="22" t="s">
         <v>21</v>
       </c>
@@ -1274,48 +1277,48 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="38"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
       <c r="L3" s="26" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
       <c r="L4" s="27" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="40"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
+      <c r="A5" s="36"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
       <c r="L5" s="19" t="s">
         <v>22</v>
       </c>
@@ -1340,30 +1343,30 @@
       </c>
       <c r="G6" s="14">
         <f>COUNTIF(G10:G59,"⏳ Pendente")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" s="15" t="s">
         <v>14</v>
       </c>
       <c r="I6" s="16">
         <f>COUNTIF(G10:G59,"🔄 Em revisão")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="19" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="40"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="40"/>
+      <c r="A7" s="36"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
       <c r="L7" s="23" t="s">
         <v>27</v>
       </c>
@@ -1403,16 +1406,16 @@
       </c>
     </row>
     <row r="9" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="40"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="40"/>
+      <c r="A9" s="36"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
     </row>
     <row r="10" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17"/>
@@ -1431,14 +1434,14 @@
       <c r="F10" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="27" t="s">
-        <v>25</v>
+      <c r="G10" s="26" t="s">
+        <v>23</v>
       </c>
       <c r="H10" s="31">
         <v>46131</v>
       </c>
       <c r="I10" s="32" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J10" s="17"/>
     </row>
@@ -1875,28 +1878,28 @@
       <c r="J39" s="17"/>
     </row>
     <row r="41" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="40"/>
-      <c r="B41" s="40"/>
-      <c r="C41" s="40"/>
-      <c r="D41" s="40"/>
-      <c r="E41" s="40"/>
-      <c r="F41" s="40"/>
-      <c r="G41" s="40"/>
-      <c r="H41" s="40"/>
-      <c r="I41" s="40"/>
-      <c r="J41" s="40"/>
+      <c r="A41" s="36"/>
+      <c r="B41" s="36"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="36"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="36"/>
+      <c r="J41" s="36"/>
     </row>
     <row r="42" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="41" t="s">
+      <c r="B42" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="C42" s="41"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="41"/>
-      <c r="F42" s="41"/>
-      <c r="G42" s="41"/>
-      <c r="H42" s="41"/>
-      <c r="I42" s="41"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="37"/>
+      <c r="H42" s="37"/>
+      <c r="I42" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/DRIVE/3. Operações/3.1 Projetos/Lista entregaveis projetos.xlsx
+++ b/DRIVE/3. Operações/3.1 Projetos/Lista entregaveis projetos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\MINDSET\DRIVE\3. Operações\3.1 Projetos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{392D1C06-36B3-4EE2-9BDB-D8AFD666CB30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A027C7-3FDE-45C8-9B53-ADE152A66F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="53">
   <si>
     <t>Nº</t>
   </si>
@@ -189,7 +189,13 @@
     <t>INDEFINIDA</t>
   </si>
   <si>
-    <t>Espera fornecedor, aguardar feeback</t>
+    <t>25001 (interno)</t>
+  </si>
+  <si>
+    <t>26003 (externo)</t>
+  </si>
+  <si>
+    <t>26002 (externo)</t>
   </si>
 </sst>
 </file>
@@ -658,9 +664,6 @@
     <xf numFmtId="0" fontId="19" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -689,6 +692,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -970,39 +976,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="38"/>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
+      <c r="A1" s="37"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
     </row>
     <row r="2" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
     </row>
     <row r="3" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="40"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
     </row>
     <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
@@ -1067,16 +1073,16 @@
       <c r="D6" s="5">
         <v>3</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="33" t="s">
+      <c r="F6" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="33" t="s">
+      <c r="G6" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="33" t="s">
+      <c r="H6" s="32" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="2"/>
@@ -1093,7 +1099,7 @@
       <c r="D7" s="4">
         <v>1</v>
       </c>
-      <c r="E7" s="34" t="s">
+      <c r="E7" s="33" t="s">
         <v>45</v>
       </c>
       <c r="F7" s="4" t="s">
@@ -1206,15 +1212,15 @@
       <c r="I14" s="6"/>
     </row>
     <row r="16" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1238,37 +1244,37 @@
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="6" max="6" width="36.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="16" customWidth="1"/>
     <col min="9" max="9" width="32.21875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="38"/>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="A1" s="37"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
     </row>
     <row r="2" spans="1:14" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
       <c r="L2" s="22" t="s">
         <v>21</v>
       </c>
@@ -1277,48 +1283,48 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="40"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
       <c r="L3" s="26" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
       <c r="L4" s="27" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="36"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
+      <c r="A5" s="35"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
       <c r="L5" s="19" t="s">
         <v>22</v>
       </c>
@@ -1328,8 +1334,8 @@
         <v>11</v>
       </c>
       <c r="C6" s="10">
-        <f>COUNTA(B10:B11)</f>
-        <v>2</v>
+        <f>COUNTA(C10:C19)</f>
+        <v>3</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>12</v>
@@ -1357,16 +1363,16 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="36"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
+      <c r="A7" s="35"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
       <c r="L7" s="23" t="s">
         <v>27</v>
       </c>
@@ -1401,21 +1407,21 @@
       <c r="L8" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="N8" s="32" t="s">
+      <c r="N8" s="31" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="36"/>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
     </row>
     <row r="10" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17"/>
@@ -1428,8 +1434,8 @@
       <c r="D10" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="29">
-        <v>26002</v>
+      <c r="E10" s="29" t="s">
+        <v>52</v>
       </c>
       <c r="F10" s="30" t="s">
         <v>34</v>
@@ -1437,11 +1443,11 @@
       <c r="G10" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="31">
-        <v>46131</v>
-      </c>
-      <c r="I10" s="32" t="s">
-        <v>50</v>
+      <c r="H10" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="I10" s="19" t="s">
+        <v>24</v>
       </c>
       <c r="J10" s="17"/>
     </row>
@@ -1456,16 +1462,18 @@
       <c r="D11" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="29">
-        <v>26003</v>
-      </c>
-      <c r="F11" s="35" t="s">
+      <c r="E11" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="34" t="s">
         <v>40</v>
       </c>
       <c r="G11" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="23"/>
+      <c r="H11" s="43">
+        <v>46143</v>
+      </c>
       <c r="I11" s="19" t="s">
         <v>26</v>
       </c>
@@ -1482,8 +1490,8 @@
       <c r="D12" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="29">
-        <v>25001</v>
+      <c r="E12" s="29" t="s">
+        <v>50</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>48</v>
@@ -1495,7 +1503,7 @@
         <v>49</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J12" s="17"/>
     </row>
@@ -1878,28 +1886,28 @@
       <c r="J39" s="17"/>
     </row>
     <row r="41" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="36"/>
-      <c r="B41" s="36"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="36"/>
-      <c r="G41" s="36"/>
-      <c r="H41" s="36"/>
-      <c r="I41" s="36"/>
-      <c r="J41" s="36"/>
+      <c r="A41" s="35"/>
+      <c r="B41" s="35"/>
+      <c r="C41" s="35"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="35"/>
+      <c r="H41" s="35"/>
+      <c r="I41" s="35"/>
+      <c r="J41" s="35"/>
     </row>
     <row r="42" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="37" t="s">
+      <c r="B42" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="C42" s="37"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="37"/>
-      <c r="G42" s="37"/>
-      <c r="H42" s="37"/>
-      <c r="I42" s="37"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="36"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/DRIVE/3. Operações/3.1 Projetos/Lista entregaveis projetos.xlsx
+++ b/DRIVE/3. Operações/3.1 Projetos/Lista entregaveis projetos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\MINDSET\DRIVE\3. Operações\3.1 Projetos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A027C7-3FDE-45C8-9B53-ADE152A66F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E17DC3-F9B4-4EB3-9F02-5F68721EFAF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -676,6 +676,9 @@
     <xf numFmtId="0" fontId="19" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="6" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -692,9 +695,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -976,39 +976,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="37"/>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
+      <c r="A1" s="38"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
     </row>
     <row r="2" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
     </row>
     <row r="3" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="39"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
     </row>
     <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
@@ -1212,15 +1212,15 @@
       <c r="I14" s="6"/>
     </row>
     <row r="16" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="42" t="s">
+      <c r="B16" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1251,30 +1251,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="37"/>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
+      <c r="A1" s="38"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
     </row>
     <row r="2" spans="1:14" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
       <c r="L2" s="22" t="s">
         <v>21</v>
       </c>
@@ -1283,48 +1283,48 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="39"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
       <c r="L3" s="26" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
       <c r="L4" s="27" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="35"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
+      <c r="A5" s="36"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
       <c r="L5" s="19" t="s">
         <v>22</v>
       </c>
@@ -1349,30 +1349,30 @@
       </c>
       <c r="G6" s="14">
         <f>COUNTIF(G10:G59,"⏳ Pendente")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="15" t="s">
         <v>14</v>
       </c>
       <c r="I6" s="16">
         <f>COUNTIF(G10:G59,"🔄 Em revisão")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="19" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="35"/>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="35"/>
+      <c r="A7" s="36"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
       <c r="L7" s="23" t="s">
         <v>27</v>
       </c>
@@ -1412,16 +1412,16 @@
       </c>
     </row>
     <row r="9" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="35"/>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="35"/>
+      <c r="A9" s="36"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
     </row>
     <row r="10" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17"/>
@@ -1468,14 +1468,14 @@
       <c r="F11" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="43">
-        <v>46143</v>
+      <c r="G11" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="35">
+        <v>46147</v>
       </c>
       <c r="I11" s="19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J11" s="17"/>
     </row>
@@ -1886,28 +1886,28 @@
       <c r="J39" s="17"/>
     </row>
     <row r="41" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="35"/>
-      <c r="B41" s="35"/>
-      <c r="C41" s="35"/>
-      <c r="D41" s="35"/>
-      <c r="E41" s="35"/>
-      <c r="F41" s="35"/>
-      <c r="G41" s="35"/>
-      <c r="H41" s="35"/>
-      <c r="I41" s="35"/>
-      <c r="J41" s="35"/>
+      <c r="A41" s="36"/>
+      <c r="B41" s="36"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="36"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="36"/>
+      <c r="J41" s="36"/>
     </row>
     <row r="42" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="36" t="s">
+      <c r="B42" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="C42" s="36"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="36"/>
-      <c r="I42" s="36"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="37"/>
+      <c r="H42" s="37"/>
+      <c r="I42" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/DRIVE/3. Operações/3.1 Projetos/Lista entregaveis projetos.xlsx
+++ b/DRIVE/3. Operações/3.1 Projetos/Lista entregaveis projetos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\MINDSET\DRIVE\3. Operações\3.1 Projetos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E17DC3-F9B4-4EB3-9F02-5F68721EFAF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C9CEDFF-3C1E-4B2C-8779-730658E698E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="55">
   <si>
     <t>Nº</t>
   </si>
@@ -196,6 +196,12 @@
   </si>
   <si>
     <t>26002 (externo)</t>
+  </si>
+  <si>
+    <t>FATURADO</t>
+  </si>
+  <si>
+    <t>Espera do cliente</t>
   </si>
 </sst>
 </file>
@@ -1342,7 +1348,7 @@
       </c>
       <c r="E6" s="12">
         <f>COUNTIF(G10:G59,"✅ Entregue")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>13</v>
@@ -1356,10 +1362,13 @@
       </c>
       <c r="I6" s="16">
         <f>COUNTIF(G10:G59,"🔄 Em revisão")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" s="19" t="s">
         <v>24</v>
+      </c>
+      <c r="N6" s="31" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1440,14 +1449,14 @@
       <c r="F10" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="19" t="s">
-        <v>49</v>
+      <c r="G10" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="35">
+        <v>46161</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="J10" s="17"/>
     </row>
@@ -1474,8 +1483,8 @@
       <c r="H11" s="35">
         <v>46147</v>
       </c>
-      <c r="I11" s="19" t="s">
-        <v>24</v>
+      <c r="I11" s="31" t="s">
+        <v>54</v>
       </c>
       <c r="J11" s="17"/>
     </row>
@@ -1503,7 +1512,7 @@
         <v>49</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J12" s="17"/>
     </row>
